--- a/b-Office-Diana/人工开发表格.xlsx
+++ b/b-Office-Diana/人工开发表格.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OneHistory\HistoryClio\2026-019-HistoryDiana\b-Office-Diana\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFADB39-EECF-453D-899B-4ABA1AA97A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD04806-64EB-4DB3-A3F5-A23BBC5A7BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3825" yWindow="4380" windowWidth="28800" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2100" yWindow="1725" windowWidth="28800" windowHeight="15435" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vulcan" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,8 @@
     <sheet name="Mercury" sheetId="5" state="hidden" r:id="rId7"/>
     <sheet name="Minerva" sheetId="4" r:id="rId8"/>
     <sheet name="Strenua" sheetId="10" r:id="rId9"/>
-    <sheet name="Apollo" sheetId="9" r:id="rId10"/>
+    <sheet name="Fama" sheetId="11" r:id="rId10"/>
+    <sheet name="Apollo" sheetId="9" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="165">
   <si>
     <t>版本号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -796,6 +797,85 @@
   <si>
     <t>strenuaV1.14 技术要求类下面的可选项删除避障和尺寸链改为ai填写技术要求（按钮和选择，按钮就是当前即执行，选择则是选上别的地方调用技术要求就ai来），ai直接用我们的模块统一接口就行让ai可以按照当前图纸信息选择技术要求为基础，（先看一下ai能不能输入图片识别如果没有升级一下）输入：当前图纸，待选技术要求标题，图纸基本信息jeson，输出应该以哪个技术要求为基础（或者没有技术要求作为基础）。选完基础以后就按照当前信息微调修改这个技术要求基础即可
 ，（注意别整段重写而只是克制的增删技术要求）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V5.15.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">janusV5.15.2小更新，将0000-000的模板模块中选择性添加的文件unused直接纳入z级文件夹，然后拉项目的时候统一不继承z级别文件夹，那么其他项目拉模板也不会拉z级文件夹和里面一坨模板，只在使用的时候复制他
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V5.15.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">janusv5.15.3小更新，当一个项目已经提交完毕，工作树已经干净了以后出现提示但是操作列并没有改为推送请修改（请观察一下这个多态有没有同样的其他情况一样修掉）分支图谱页面左侧的main之类的全部删除掉别挡住泳道。Janus页面顶栏添加”排列“多态选择box，第一态是编号（现状）第二态是”操作“（按从提交-拉取）排列
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1.14.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">strenuaV1.14.1 小更新，请你观察当前开着的SW实例，图纸中6x孔和4x孔都只展现了3个和2个，修改孔标注指令当识别到对面孔位置与当前一致且被识别为同一种孔的时候在孔标注中添加（含对面），否则要在投影视图中开新视图（这个应该已经做过相关代码），并如我修改的所示，当孔识别到一个视图中所有元素和孔都是轴对称的，添加对称轴并以对称轴为基准做标注（不是从对称轴开始而是直接标对称轴两侧孔的距离）一定注意，此时以单一面为基准的那种同一种孔可以互相标不同孔不能互相标的标准仍然存在.
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1.14.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">strenuaV1.14.2 纠错，现在我们发现我们的圆角标注指令事实上承担了所有圆的标注，所以请添加圆角标注中圆心的标注，首先如果一个圆弧两端都直接与线条相切，则这个圆的圆心不用标注，如果一个圆的圆弧与两端的直线都不相切，则这个圆的圆心需要标2个尺寸（按照孔的那个基准一致的）。如果一个圆的圆弧与两端直线有一个相切则是最麻烦的一种情况，若相切的那条直线与两个基准直线都不平行，那么只需要添加一个位置尺寸（无论水平还是竖直）如果相切的那个直线平行于水平/竖直的尺寸基准，则以平行的基准为尺寸的那个尺寸不能标，只能以另外一个基准去标注.我们直接改掉圆角命令改为“圆弧”，这次添加的圆弧圆心位置为新的指令，也都纳入自动标注流程
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">minerva V4.13更新 现在遇到新的问题，我们的属性整备刚刚试用下来遇到一堆报错但是功能是ok的，现在请把这些报错处理一下，另外属性整备的功能现在如果不填写图号会不会把原理的图号顶掉看看，不能顶掉，第三是我们的材料依然有误比如现在的实例中材料依旧只显示SW-Material而不是真正的材料，第四是当我们把一个东西改为外购间以后，其子装配零件自动不在表格内显示，另外现在按规定，所有的外购件改完以后位置统一存在“外购件”的次级文件夹中。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V4.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v1.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">strenuaV1.15 试用细节打磨 ，1:倒角标注没做避障避障做一下 2：直接一键出图时，图纸的名称需要改为和所引用的零件一致，这个功能直接加到新建工程图里面，3：同一个孔标注在不同视图里面会被重复标注，这个必须删除一个（位置也是，这个现行很罕见，但是比如顶视图和底视图都存在的时候会有）4：沉孔在标注的背面的时候优先选择能表现沉孔的视图（由于我们的视图选择会优先选盲销孔所以展现沉孔不是最优选择，有时只能在反面标沉孔，那么就要在沉孔那一行添加（反面））5：我不清楚是图纸问题还是代码问题，c0.5的倒角有标注吗，我们默认不标注的倒角是c1 6：把那个公差仅对销孔的规则写（仅销孔）改为（公差仅对销孔）6：倒圆或者倒角的指令拆分为独立的类
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孔位尺寸的避障不管图框里的修改栏、图号框，移动底板上视图的尺寸会压上去。
+一键出图的主视图方向不对：滑动板回执说「*前视，沿 Z 看」，实际建出来是从 +X 看，板面跑到了下面的投影视图。
+3:检查别依赖表注侧，而是独立写一个检查算法检查是否有东西没标注，检查完以后弹出（那些线没标高亮，并弹窗显示那些标注为小数点后2位警告，这种一般都不允许存在）
+4:ai改技术要求里面无需写由下角输入的相关内容（他已经是写右下角了）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1.17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">一键区添加一键出钣金和一键出框架，钣金可以参考C:\OneHistory\HistoryClio\2026-025-实验室测绘\a20-绘图\b-Module-SW 里面的WTJYQ-04 框架参考WTJYQ-04-01 这2个不用单独的类，而是只有在一键类里面的指令，框架更简单，只标注外轮廓和轴测图的采用xx铝型材 钣金则需要标孔和外轮廓，但是需要算法排除钣金折弯产生的那个外部线条（那个线不能标注，会产生2位小数而且也没必要标注）最后是一键出加工件（其他情况）（三个在一键出图下面另起一行）。孔标注全流程里面还有外轮廓标注相关代码，把他移出孔类移动到基础类里面，最后孔类再加一个方形槽标注，用于标注方形槽的位置，相关图纸在WTJYQ-04-02，stewnuaV1.17
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对称轴标注有bug，这是sw的原因，标完以后要看一下对称轴是不是贯穿全图，有时候选的对称的边
+短会让对称轴无贯穿全图，这个需要调整</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1292,6 +1372,16 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E250F64-35BD-4966-B94B-27C5CCFFE651}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B0886C-D541-4B94-A535-5F9B5F3A7562}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1696,7 +1786,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73FAE02E-7314-4E6D-B0E9-65ED684E18A3}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="70.75" customWidth="1"/>
@@ -1720,12 +1810,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="57" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="D3">
         <v>111</v>
@@ -1733,10 +1823,10 @@
     </row>
     <row r="4" spans="1:4" ht="57" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="D4">
         <v>111</v>
@@ -1744,65 +1834,65 @@
     </row>
     <row r="5" spans="1:4" ht="57" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="57" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="57" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D5">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="114" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+      <c r="D7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="114" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D6">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+      <c r="D8">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D7">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
+      <c r="D9">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="D8">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="128.25" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="D10">
         <v>111</v>
@@ -1810,21 +1900,21 @@
     </row>
     <row r="11" spans="1:4" ht="128.25" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="D11">
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D12">
         <v>111</v>
@@ -1832,23 +1922,45 @@
     </row>
     <row r="13" spans="1:4" ht="128.25" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D13">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
+      <c r="D15">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
         <v>5</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C16" t="s">
         <v>6</v>
       </c>
-      <c r="D14">
+      <c r="D16">
         <v>111</v>
       </c>
     </row>
@@ -1990,8 +2102,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C3" s="1"/>
+    <row r="3" spans="1:4" ht="114" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:4" ht="114" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -2001,7 +2121,7 @@
         <v>119</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
@@ -2133,29 +2253,26 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90F44E87-499B-464F-80FE-D9ED4838A60C}">
-  <dimension ref="A2:C14"/>
+  <dimension ref="A2:C20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="84.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="114" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="C3">
         <v>111</v>
@@ -2163,122 +2280,188 @@
     </row>
     <row r="4" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="114" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="114" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C4">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="C10">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C5">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="C11">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C6">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="57" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="C12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="57" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C7">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="57" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="C13">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="57" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>135</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C8">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="C14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C9">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="C15">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C10">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="57" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="C16">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="57" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>126</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C11">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="C17">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C12">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="C18">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C13">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="C19">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C14">
+      <c r="C20">
         <v>111</v>
       </c>
     </row>

--- a/b-Office-Diana/人工开发表格.xlsx
+++ b/b-Office-Diana/人工开发表格.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OneHistory\HistoryClio\2026-019-HistoryDiana\b-Office-Diana\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD04806-64EB-4DB3-A3F5-A23BBC5A7BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AE136F-649C-41E0-86B7-C0779EB3D0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="1725" windowWidth="28800" windowHeight="15435" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vulcan" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="173">
   <si>
     <t>版本号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -874,8 +874,42 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>V4.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1:那么minerva的打包把步骤拆开作为可选项在底下声明一个开关。外购件除了品牌查询以外如果名称为空的话，把名称也写入进去，最后是外购件设置的排序，把排序做一下，SW左侧的显示中，上面的外购件写入到上方，下面的外购件如果有重叠在上方添加数量，否则写下方.最后是ai查品牌效果太差了，我们申请一个Gemini的api来查，他应该更准如果有带有网络搜索的api的话
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V4.17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V8.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>对称轴标注有bug，这是sw的原因，标完以后要看一下对称轴是不是贯穿全图，有时候选的对称的边
-短会让对称轴无贯穿全图，这个需要调整</t>
+短会让对称轴无贯穿全图，这个需要调整 标注优先左下脚，左下空间不够可以网上出头，宽度不够宽的那一行可以按宽度换行，现在标注很容易就往右下退化方案走，视图标注在基准不变的情况下，可以放下侧和右侧，我们评判放哪里的标准是，放上测和放下侧哪里引线长度最小？ 于是别做上下侧负载均衡的算法，因为标注越多引线天然越长，负载均衡是天然的。还有，ai改技术要求直接退化了，现在我发现ai会乱加东西，改成可以选技术要求，但是只能删除条目，不能添加条目，不能修改条目</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:属性整备和打包里面的名称和图号都优先以属性为准，而不是以名称为准</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V4.17.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:Gemini还是无法使用，那还是改为原来的，然后选下面的步骤选项改成一行清单按钮取名简单一些，改名机加单，外购单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">轴侧图设置为带虚线版本的，另外重点提升一下视图选择的门禁，只要其他视图有元素未被展示，必须把视图显示
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1266,7 +1300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="64" customWidth="1"/>
@@ -1287,34 +1321,28 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D3">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
+      <c r="D4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>3</v>
-      </c>
-      <c r="D4">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="D5">
         <v>111</v>
@@ -1322,45 +1350,56 @@
     </row>
     <row r="6" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D6">
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D7">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
+      <c r="D8">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D8">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
+      <c r="D9">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>111</v>
       </c>
     </row>
@@ -2081,7 +2120,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BED43ADA-9453-4EFA-8E43-B7E94E813FBB}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="62.375" customWidth="1"/>
@@ -2102,146 +2141,179 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="114" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>156</v>
+        <v>170</v>
+      </c>
+      <c r="C3" t="s">
+        <v>169</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="114" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="114" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="114" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D4">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+      <c r="D7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D5">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="57" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+      <c r="D8">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="57" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D6">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+      <c r="D9">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D7">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="114" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
+      <c r="D10">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="114" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D8">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="128.25" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
+      <c r="D11">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D9">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="156.75" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
+      <c r="D12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D10">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="242.25" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
+      <c r="D13">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="242.25" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D11">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="156.75" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
+      <c r="D14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D12">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
+      <c r="D15">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D13">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
+      <c r="D16">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
         <v>7</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C17" t="s">
         <v>6</v>
       </c>
-      <c r="D14">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
+      <c r="D17">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
         <v>46</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C18" t="s">
         <v>47</v>
       </c>
-      <c r="D15">
+      <c r="D18">
         <v>111</v>
       </c>
     </row>
@@ -2253,48 +2325,45 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90F44E87-499B-464F-80FE-D9ED4838A60C}">
-  <dimension ref="A2:C20"/>
+  <dimension ref="A2:C21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="84.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="114" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="114" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C3">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="C4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="C4">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="114" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="C5">
         <v>111</v>
@@ -2302,87 +2371,87 @@
     </row>
     <row r="6" spans="1:3" ht="114" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="114" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>154</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C6">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="C7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>152</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C7">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="C8">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C8">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="C9">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>144</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C9">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="C10">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C10">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="C11">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>140</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C11">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="C12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="C12">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="57" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="C13">
         <v>111</v>
@@ -2390,78 +2459,89 @@
     </row>
     <row r="14" spans="1:3" ht="57" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="57" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>135</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C14">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="C15">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>133</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C15">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="C16">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>131</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C16">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="57" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="C17">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="57" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>126</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C17">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="C18">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>124</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C18">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="C19">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>122</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C19">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="C20">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>121</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C20">
+      <c r="C21">
         <v>111</v>
       </c>
     </row>

--- a/b-Office-Diana/人工开发表格.xlsx
+++ b/b-Office-Diana/人工开发表格.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OneHistory\HistoryClio\2026-019-HistoryDiana\b-Office-Diana\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AE136F-649C-41E0-86B7-C0779EB3D0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAFF752-6E08-4B45-B4D6-6F17C3275C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vulcan" sheetId="1" r:id="rId1"/>
@@ -887,10 +887,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>V8.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>对称轴标注有bug，这是sw的原因，标完以后要看一下对称轴是不是贯穿全图，有时候选的对称的边
 短会让对称轴无贯穿全图，这个需要调整 标注优先左下脚，左下空间不够可以网上出头，宽度不够宽的那一行可以按宽度换行，现在标注很容易就往右下退化方案走，视图标注在基准不变的情况下，可以放下侧和右侧，我们评判放哪里的标准是，放上测和放下侧哪里引线长度最小？ 于是别做上下侧负载均衡的算法，因为标注越多引线天然越长，负载均衡是天然的。还有，ai改技术要求直接退化了，现在我发现ai会乱加东西，改成可以选技术要求，但是只能删除条目，不能添加条目，不能修改条目</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -910,6 +906,10 @@
   <si>
     <t xml:space="preserve">轴侧图设置为带虚线版本的，另外重点提升一下视图选择的门禁，只要其他视图有元素未被展示，必须把视图显示
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V5.16</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1321,11 +1321,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>167</v>
-      </c>
-    </row>
     <row r="4" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>97</v>
@@ -1825,7 +1820,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73FAE02E-7314-4E6D-B0E9-65ED684E18A3}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="70.75" customWidth="1"/>
@@ -1849,23 +1844,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="D3">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="57" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>149</v>
       </c>
       <c r="D4">
         <v>111</v>
@@ -1873,10 +1862,10 @@
     </row>
     <row r="5" spans="1:4" ht="57" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="D5">
         <v>111</v>
@@ -1884,10 +1873,10 @@
     </row>
     <row r="6" spans="1:4" ht="57" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D6">
         <v>111</v>
@@ -1895,111 +1884,122 @@
     </row>
     <row r="7" spans="1:4" ht="57" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="57" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D7">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="114" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
+      <c r="D8">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="114" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D8">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
+      <c r="D9">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D9">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
+      <c r="D10">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D10">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="128.25" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
+      <c r="D11">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D11">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
+      <c r="D12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D12">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="128.25" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
+      <c r="D13">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D13">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
+      <c r="D14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D14">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="128.25" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
+      <c r="D15">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D15">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
+      <c r="D16">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
         <v>5</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>6</v>
       </c>
-      <c r="D16">
+      <c r="D17">
         <v>111</v>
       </c>
     </row>
@@ -2143,13 +2143,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -2157,7 +2157,7 @@
         <v>166</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D4">
         <v>111</v>
@@ -2333,7 +2333,7 @@
   <sheetData>
     <row r="2" spans="1:3" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="85.5" x14ac:dyDescent="0.2">
@@ -2341,7 +2341,7 @@
         <v>163</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C3">
         <v>111</v>
